--- a/excel/Profitus Rima.xlsx
+++ b/excel/Profitus Rima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Profitus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02549EDE-7DFA-4C20-8BFF-65DD21C0B8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F648BF-CFED-45EA-B4A2-F32AE67E855F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,20 +492,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -738,6 +724,20 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1246,6 +1246,9 @@
     <sheetNames>
       <sheetName val="Overview"/>
       <sheetName val="Pinigai"/>
+      <sheetName val="Namas Laipu 2, Jūrmala"/>
+      <sheetName val="Daugiabutis Brivibas 140, Ryga"/>
+      <sheetName val="Daugiabučiai Lietaviškių g."/>
       <sheetName val="Senvagės loftai, Panevėžys VIII"/>
       <sheetName val="Dvibučių kvartalas Kauno r. II"/>
       <sheetName val="Molėtų Oazė XII"/>
@@ -1272,21 +1275,9 @@
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
-      <sheetData sheetId="4">
-        <row r="2">
-          <cell r="AA2" t="str">
-            <v/>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
-      <sheetData sheetId="6">
-        <row r="2">
-          <cell r="AA2" t="str">
-            <v/>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="6"/>
       <sheetData sheetId="7">
         <row r="2">
           <cell r="AA2" t="str">
@@ -1294,13 +1285,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="8">
-        <row r="2">
-          <cell r="AA2" t="str">
-            <v>+</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="8"/>
       <sheetData sheetId="9">
         <row r="2">
           <cell r="AA2" t="str">
@@ -1315,13 +1300,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="11">
-        <row r="2">
-          <cell r="AA2" t="str">
-            <v/>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="11"/>
       <sheetData sheetId="12">
         <row r="2">
           <cell r="AA2" t="str">
@@ -1336,38 +1315,23 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15">
+      <sheetData sheetId="14">
         <row r="2">
           <cell r="AA2" t="str">
             <v/>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="16">
-        <row r="2">
-          <cell r="AA2" t="str">
-            <v/>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="17">
-        <row r="2">
-          <cell r="AA2" t="str">
-            <v/>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="18">
-        <row r="2">
-          <cell r="AA2" t="str">
-            <v/>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
       <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1825,7 +1789,7 @@
       </c>
       <c r="R3" s="5">
         <f>U3-P3</f>
-        <v>2.9099999999999682</v>
+        <v>7.7799999999999727</v>
       </c>
       <c r="S3" s="5">
         <f>SUM(L3:L200)</f>
@@ -1833,25 +1797,25 @@
       </c>
       <c r="T3" s="5">
         <f>SUM(M3:M200)</f>
-        <v>20.76</v>
+        <v>25.630000000000003</v>
       </c>
       <c r="U3" s="5">
         <f>O3+T3+Q3</f>
-        <v>669.71</v>
+        <v>674.58</v>
       </c>
       <c r="V3" s="5">
         <f>U3-O3</f>
-        <v>45.759999999999991</v>
+        <v>50.629999999999995</v>
       </c>
       <c r="W3" s="14">
         <f>(U3-O3)/O3</f>
-        <v>7.3339209872585923E-2</v>
+        <v>8.1144322461735696E-2</v>
       </c>
       <c r="X3" s="14">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.12797755599021912</v>
-      </c>
-      <c r="AC3" s="9" t="str">
+        <v>0.12409856915473938</v>
+      </c>
+      <c r="AC3" s="5" t="str">
         <f ca="1">'Senvagės loftai, Panevėžys IV'!AA2</f>
         <v/>
       </c>
@@ -1951,11 +1915,11 @@
       </c>
       <c r="J5" s="9">
         <f ca="1">'Butai centrinėje Vilniaus dal.'!B13</f>
-        <v>-8</v>
+        <v>-37</v>
       </c>
       <c r="K5" s="9">
         <f ca="1">'Butai centrinėje Vilniaus dal.'!S3</f>
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="L5" s="5">
         <f>'Butai centrinėje Vilniaus dal.'!N3</f>
@@ -2008,7 +1972,7 @@
       </c>
       <c r="J6" s="9">
         <f ca="1">'Butas Didlaukio g., Vilnius II'!B13</f>
-        <v>258</v>
+        <v>229</v>
       </c>
       <c r="K6" s="9" t="str">
         <f ca="1">'Butas Didlaukio g., Vilnius II'!S3</f>
@@ -2023,7 +1987,7 @@
         <v>2.87</v>
       </c>
       <c r="AC6" s="9" t="str">
-        <f>'[1]Elfa loftai II'!AA2</f>
+        <f ca="1">'Butas Didlaukio g., Vilnius II'!AA2</f>
         <v/>
       </c>
     </row>
@@ -2065,11 +2029,11 @@
       </c>
       <c r="J7" s="9">
         <f ca="1">'Daugiabutis Druskininkuose V'!B13</f>
-        <v>239</v>
-      </c>
-      <c r="K7" s="9">
+        <v>210</v>
+      </c>
+      <c r="K7" s="9" t="str">
         <f ca="1">'Daugiabutis Druskininkuose V'!S3</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="L7" s="5">
         <f>'Daugiabutis Druskininkuose V'!N3</f>
@@ -2077,11 +2041,11 @@
       </c>
       <c r="M7" s="5">
         <f>'Daugiabutis Druskininkuose V'!P3</f>
-        <v>0</v>
+        <v>2.3899999999999997</v>
       </c>
       <c r="AC7" s="9" t="str">
         <f ca="1">'Daugiabutis Druskininkuose V'!AA2</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
@@ -2122,7 +2086,7 @@
       </c>
       <c r="J8" s="9">
         <f ca="1">'Druskonio Perlai, Druskininkai '!B13</f>
-        <v>293</v>
+        <v>264</v>
       </c>
       <c r="K8" s="9" t="str">
         <f ca="1">'Druskonio Perlai, Druskininkai '!S3</f>
@@ -2134,7 +2098,7 @@
       </c>
       <c r="M8" s="5">
         <f>'Druskonio Perlai, Druskininkai '!P3</f>
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC8" s="5" t="str">
         <f ca="1">'Druskonio Perlai, Druskininkai '!AA2</f>
@@ -2179,7 +2143,7 @@
       </c>
       <c r="J9" s="9">
         <f ca="1">'Huberto Namai, Trakų r. VII'!B13</f>
-        <v>349</v>
+        <v>320</v>
       </c>
       <c r="K9" s="9" t="str">
         <f ca="1">'Huberto Namai, Trakų r. VII'!S3</f>
@@ -2236,7 +2200,7 @@
       </c>
       <c r="J10" s="9">
         <f ca="1">'Dvibutis prie Neries, Vilniaus '!B13</f>
-        <v>349</v>
+        <v>320</v>
       </c>
       <c r="K10" s="9" t="str">
         <f ca="1">'Dvibutis prie Neries, Vilniaus '!S3</f>
@@ -2271,10 +2235,7 @@
       <c r="K11" s="9"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
-      <c r="AC11" s="9" t="str">
-        <f>'[1]Dvibutis Klevų g.'!AA2</f>
-        <v/>
-      </c>
+      <c r="AC11" s="9"/>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
@@ -2292,10 +2253,7 @@
       <c r="K12" s="9"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
-      <c r="AC12" s="9" t="str">
-        <f>'[1]Dvibutis Upelio g., Vilniaus r.'!AA2</f>
-        <v/>
-      </c>
+      <c r="AC12" s="9"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
@@ -2592,14 +2550,14 @@
       <formula>AND($G3&gt;0,$G3=$L3)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC4">
+  <conditionalFormatting sqref="AC3:AC4">
     <cfRule type="expression" dxfId="38" priority="8">
       <formula>$AC$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC4:AC5">
+  <conditionalFormatting sqref="AC3:AC5">
     <cfRule type="expression" dxfId="37" priority="5">
-      <formula>AND($G4&gt;0,$G4=$L4)</formula>
+      <formula>AND($G3&gt;0,$G3=$L3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC5">
@@ -2607,20 +2565,20 @@
       <formula>#REF!="+"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AC8:AC10">
+    <cfRule type="expression" dxfId="35" priority="1">
+      <formula>$AC8="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="2">
+      <formula>AND($G8&gt;0,$G8=$L8)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AC20">
-    <cfRule type="expression" dxfId="35" priority="9">
+    <cfRule type="expression" dxfId="33" priority="9">
       <formula>AND($G20&gt;0,$G20=$L20)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="10">
+    <cfRule type="expression" dxfId="32" priority="10">
       <formula>$AC20="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC8:AC10">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>$AC8="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>AND($G8&gt;0,$G8=$L8)</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -3782,20 +3740,20 @@
     <mergeCell ref="S1:S2"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>$AA$2="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="3" priority="7">
+    <cfRule type="expression" dxfId="1" priority="7">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="2" priority="8">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3847,7 +3805,7 @@
       </c>
       <c r="L1" s="20">
         <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>0.12797755599021912</v>
+        <v>0.12409856915473938</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -5313,14 +5271,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="10">
         <f ca="1">TODAY()</f>
-        <v>46266</v>
+        <v>46295</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
       <c r="K200" s="5">
         <f>Overview!U3</f>
-        <v>669.71</v>
+        <v>674.58</v>
       </c>
     </row>
   </sheetData>
@@ -5779,7 +5737,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>349</v>
+        <v>320</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -6436,20 +6394,20 @@
     <mergeCell ref="S1:S2"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="31" priority="1">
       <formula>$AA$2="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="2">
+    <cfRule type="expression" dxfId="30" priority="2">
       <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="31" priority="3">
+    <cfRule type="expression" dxfId="29" priority="3">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="30" priority="4">
+    <cfRule type="expression" dxfId="28" priority="4">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6908,7 +6866,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>349</v>
+        <v>320</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -7565,20 +7523,20 @@
     <mergeCell ref="S1:S2"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="29" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>$AA$2="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="2">
+    <cfRule type="expression" dxfId="26" priority="2">
       <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="27" priority="3">
+    <cfRule type="expression" dxfId="25" priority="3">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="26" priority="4">
+    <cfRule type="expression" dxfId="24" priority="4">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7679,13 +7637,21 @@
       <c r="F2" s="5">
         <v>2.48</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="9" t="str">
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="10">
+        <v>46295</v>
+      </c>
+      <c r="K2" s="9">
         <f>IF(J2&gt;0,J2-D2,"")</f>
-        <v/>
+        <v>-7</v>
       </c>
       <c r="M2" s="13" t="s">
         <v>39</v>
@@ -7753,7 +7719,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q3" s="14" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
@@ -7769,11 +7735,11 @@
       </c>
       <c r="Y3" s="10">
         <f>J2</f>
-        <v>0</v>
+        <v>46295</v>
       </c>
       <c r="Z3" s="5">
         <f>G2+H2+I2</f>
-        <v>0</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -8037,7 +8003,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>293</v>
+        <v>264</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -8676,7 +8642,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="3"/>
@@ -8694,20 +8660,20 @@
     <mergeCell ref="S1:S2"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="25" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>$AA$2="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="2">
+    <cfRule type="expression" dxfId="22" priority="2">
       <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="23" priority="7">
+    <cfRule type="expression" dxfId="21" priority="7">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="22" priority="8">
+    <cfRule type="expression" dxfId="20" priority="8">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8808,13 +8774,21 @@
       <c r="F2" s="5">
         <v>2.2599999999999998</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="9" t="str">
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="J2" s="10">
+        <v>46276</v>
+      </c>
+      <c r="K2" s="9">
         <f>IF(J2&gt;0,J2-D2,"")</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="M2" s="13" t="s">
         <v>39</v>
@@ -8841,7 +8815,7 @@
       </c>
       <c r="AA2" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -8882,7 +8856,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>0</v>
+        <v>2.3899999999999997</v>
       </c>
       <c r="Q3" s="14" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
@@ -8892,17 +8866,17 @@
         <f>IF(M3=N3,B14,"")</f>
         <v/>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Y3" s="10">
         <f>J2</f>
-        <v>0</v>
+        <v>46276</v>
       </c>
       <c r="Z3" s="5">
         <f>G2+H2+I2</f>
-        <v>0</v>
+        <v>2.3899999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -9166,7 +9140,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -9805,11 +9779,11 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -9823,20 +9797,20 @@
     <mergeCell ref="S1:S2"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>$AA$2="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="2">
+    <cfRule type="expression" dxfId="18" priority="2">
       <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="19" priority="7">
+    <cfRule type="expression" dxfId="17" priority="7">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="18" priority="8">
+    <cfRule type="expression" dxfId="16" priority="8">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10303,7 +10277,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>258</v>
+        <v>229</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -10960,20 +10934,20 @@
     <mergeCell ref="S1:S2"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>$AA$2="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="15" priority="11">
+    <cfRule type="expression" dxfId="13" priority="11">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="14" priority="12">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10985,7 +10959,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1447860C-6895-4117-8CA4-0B2D4DA1EC46}">
   <sheetPr>
-    <tabColor rgb="FFFFC000"/>
+    <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11171,7 +11145,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="Y3" s="10">
         <f>J2</f>
@@ -11437,7 +11411,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-8</v>
+        <v>-37</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -12094,20 +12068,20 @@
     <mergeCell ref="S1:S2"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>$AA$2="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="11" priority="11">
+    <cfRule type="expression" dxfId="9" priority="11">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="10" priority="12">
+    <cfRule type="expression" dxfId="8" priority="12">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13260,20 +13234,20 @@
     <mergeCell ref="S1:S2"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>$AA$2="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="7" priority="9">
+    <cfRule type="expression" dxfId="5" priority="9">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="6" priority="10">
+    <cfRule type="expression" dxfId="4" priority="10">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/excel/Profitus Rima.xlsx
+++ b/excel/Profitus Rima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Profitus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F648BF-CFED-45EA-B4A2-F32AE67E855F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8763629B-EB39-43F9-B641-E4F59350721E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="X3" s="14">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.12409856915473938</v>
+        <v>0.11799659132957457</v>
       </c>
       <c r="AC3" s="5" t="str">
         <f ca="1">'Senvagės loftai, Panevėžys IV'!AA2</f>
@@ -1915,11 +1915,11 @@
       </c>
       <c r="J5" s="9">
         <f ca="1">'Butai centrinėje Vilniaus dal.'!B13</f>
-        <v>-37</v>
+        <v>-49</v>
       </c>
       <c r="K5" s="9">
         <f ca="1">'Butai centrinėje Vilniaus dal.'!S3</f>
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="L5" s="5">
         <f>'Butai centrinėje Vilniaus dal.'!N3</f>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="J6" s="9">
         <f ca="1">'Butas Didlaukio g., Vilnius II'!B13</f>
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="K6" s="9" t="str">
         <f ca="1">'Butas Didlaukio g., Vilnius II'!S3</f>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="J7" s="9">
         <f ca="1">'Daugiabutis Druskininkuose V'!B13</f>
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="K7" s="9" t="str">
         <f ca="1">'Daugiabutis Druskininkuose V'!S3</f>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="J8" s="9">
         <f ca="1">'Druskonio Perlai, Druskininkai '!B13</f>
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="K8" s="9" t="str">
         <f ca="1">'Druskonio Perlai, Druskininkai '!S3</f>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="J9" s="9">
         <f ca="1">'Huberto Namai, Trakų r. VII'!B13</f>
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="K9" s="9" t="str">
         <f ca="1">'Huberto Namai, Trakų r. VII'!S3</f>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="J10" s="9">
         <f ca="1">'Dvibutis prie Neries, Vilniaus '!B13</f>
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="K10" s="9" t="str">
         <f ca="1">'Dvibutis prie Neries, Vilniaus '!S3</f>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="L1" s="20">
         <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>0.12409856915473938</v>
+        <v>0.11799659132957457</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -5271,7 +5271,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="10">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46307</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -10277,7 +10277,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -11145,7 +11145,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="Y3" s="10">
         <f>J2</f>
@@ -11411,7 +11411,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-37</v>
+        <v>-49</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -12361,7 +12361,7 @@
       <c r="H5" s="5">
         <v>0.96</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="10">
